--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ג'קו אייזנברג ורון נשר – קיווינו</v>
+        <v>קרולינה ואורי בראונר כנרות – תפילה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%a7%d7%95-%d7%90%d7%99%d7%99%d7%96%d7%a0%d7%91%d7%a8%d7%92-%d7%95%d7%a8%d7%95%d7%9f-%d7%a0%d7%a9%d7%a8-%d7%a7%d7%99%d7%95%d7%95%d7%99%d7%a0%d7%95/</v>
+        <v>https://yosmusic.com/%d7%a7%d7%a8%d7%95%d7%9c%d7%99%d7%a0%d7%94-%d7%95%d7%90%d7%95%d7%a8%d7%99-%d7%91%d7%a8%d7%90%d7%95%d7%a0%d7%a8-%d7%9b%d7%a0%d7%a8%d7%95%d7%aa-%d7%aa%d7%a4%d7%99%d7%9c%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "קיווינו” של ג'קו אייזנברג ורון נשר הוא בלדת רוק טעונה שמצליחה להחזיק בו־זמנית גם כאב אישי וגם אמירה חברתית רחבה יותר. זה שיר שלא מציע פתרון ברור. במקום להכריז “יהיה טוב”, הוא נשאר בתוך חוסר הוודאות, בתוך העייפות של</v>
+        <v>השיר "תפילה” של קרולינה הוא מהסוג שלא מנסה להרשים בכוח אלא לחלחל לאט. זוהי בלדת פופ־גרוב עדינה ואינטימית, שנשענת פחות על דרמה גדולה ויותר על אמת רגשית חשופה. קרולינה נשארת כאן מאוד “היא”: סאונד חם, אנושי, מלא נשימה ונוכחות, עם</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ג'קו אייזנברג ורון נשר – קיווינו</v>
+        <v>קרולינה ואורי בראונר כנרות – תפילה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קרולינה ואורי בראונר כנרות – תפילה</v>
+        <v>בן ארצי – ישראל</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a7%d7%a8%d7%95%d7%9c%d7%99%d7%a0%d7%94-%d7%95%d7%90%d7%95%d7%a8%d7%99-%d7%91%d7%a8%d7%90%d7%95%d7%a0%d7%a8-%d7%9b%d7%a0%d7%a8%d7%95%d7%aa-%d7%aa%d7%a4%d7%99%d7%9c%d7%94/</v>
+        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%90%d7%a8%d7%a6%d7%99-%d7%99%d7%a9%d7%a8%d7%90%d7%9c/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "תפילה” של קרולינה הוא מהסוג שלא מנסה להרשים בכוח אלא לחלחל לאט. זוהי בלדת פופ־גרוב עדינה ואינטימית, שנשענת פחות על דרמה גדולה ויותר על אמת רגשית חשופה. קרולינה נשארת כאן מאוד “היא”: סאונד חם, אנושי, מלא נשימה ונוכחות, עם</v>
+        <v>השיר "ישראל” של בן ארצי בנוי כעל פרדוקס רגשי: אהבה עמוקה למדינה לצד תחושת אכזבה קשה ממנה. זה לא שיר מחאה זועם או מהפכני, אלא שיר של אדם שמרגיש שייך – ולכן גם פגוע. דווקא בגלל הטון הפשוט והישיר שלו,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קרולינה ואורי בראונר כנרות – תפילה</v>
+        <v>בן ארצי – ישראל</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בן ארצי – ישראל</v>
+        <v>מאיה בוסקילה – קח אותי לרקוד</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%90%d7%a8%d7%a6%d7%99-%d7%99%d7%a9%d7%a8%d7%90%d7%9c/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%99%d7%94-%d7%91%d7%95%d7%a1%d7%a7%d7%99%d7%9c%d7%94-%d7%a7%d7%97-%d7%90%d7%95%d7%aa%d7%99-%d7%9c%d7%a8%d7%a7%d7%95%d7%93/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-17</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "ישראל” של בן ארצי בנוי כעל פרדוקס רגשי: אהבה עמוקה למדינה לצד תחושת אכזבה קשה ממנה. זה לא שיר מחאה זועם או מהפכני, אלא שיר של אדם שמרגיש שייך – ולכן גם פגוע. דווקא בגלל הטון הפשוט והישיר שלו,</v>
+        <v>מאיה בוסקילה לוקחת נוסחה מוכרת של פופ־דאנס ים־תיכוני, והופכת אותה להצהרה רגשית על פחד, תשוקה וחופש אישי. זה שיר שנשמע קודם כול כמו להיט מועדונים גדול, אבל מתחת לביט הכבד והדרמה הווקאלית מסתתר סיפור על אנשים שמפחדים לאהוב בגלוי. הקונפליקט</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בן ארצי – ישראל</v>
+        <v>מאיה בוסקילה – קח אותי לרקוד</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מאיה בוסקילה – קח אותי לרקוד</v>
+        <v>מיקה משה ואלי חולי – כמו פעם</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%99%d7%94-%d7%91%d7%95%d7%a1%d7%a7%d7%99%d7%9c%d7%94-%d7%a7%d7%97-%d7%90%d7%95%d7%aa%d7%99-%d7%9c%d7%a8%d7%a7%d7%95%d7%93/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a7%d7%94-%d7%9e%d7%a9%d7%94-%d7%95%d7%90%d7%9c%d7%99-%d7%97%d7%95%d7%9c%d7%99-%d7%9b%d7%9e%d7%95-%d7%a4%d7%a2%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מאיה בוסקילה לוקחת נוסחה מוכרת של פופ־דאנס ים־תיכוני, והופכת אותה להצהרה רגשית על פחד, תשוקה וחופש אישי. זה שיר שנשמע קודם כול כמו להיט מועדונים גדול, אבל מתחת לביט הכבד והדרמה הווקאלית מסתתר סיפור על אנשים שמפחדים לאהוב בגלוי. הקונפליקט</v>
+        <v>מיקה משה ואלי חולי שרים דואט שבנוי כמעט כמו מסע רגשי מדורג – גם מוזיקלית וגם טקסטואלית. הוא מתחיל באינטימיות שקטה, מטפס לכאב מתפרץ, ואז נסחף למיד־טמפו רגשי שמרגיש כמו ניסיון להיאחז בזיכרון לפני שהוא נעלם. הכניסה של אלי חולי</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מאיה בוסקילה – קח אותי לרקוד</v>
+        <v>מיקה משה ואלי חולי – כמו פעם</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מיקה משה ואלי חולי – כמו פעם</v>
+        <v>שלומית אהרון – פיסות אהבה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a7%d7%94-%d7%9e%d7%a9%d7%94-%d7%95%d7%90%d7%9c%d7%99-%d7%97%d7%95%d7%9c%d7%99-%d7%9b%d7%9e%d7%95-%d7%a4%d7%a2%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%9e%d7%99%d7%aa-%d7%90%d7%94%d7%a8%d7%95%d7%9f-%d7%a4%d7%99%d7%a1%d7%95%d7%aa-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מיקה משה ואלי חולי שרים דואט שבנוי כמעט כמו מסע רגשי מדורג – גם מוזיקלית וגם טקסטואלית. הוא מתחיל באינטימיות שקטה, מטפס לכאב מתפרץ, ואז נסחף למיד־טמפו רגשי שמרגיש כמו ניסיון להיאחז בזיכרון לפני שהוא נעלם. הכניסה של אלי חולי</v>
+        <v>שלומית אהרון מגישה ב־"פיסות אהבה" שיר שנשען על מסורת הפופ המלודי הקלאסי של שנות ה־70 וה־80. . זהו שיר שמחבר בין אסתטיקה “אולד סקול” לבין חרדה קיומית,  והחיבור הזה הוא מקור הכוח שלו. צליל האקורדיון בפתיחה מייצר אווירת שנסון אירופי</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,50 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מיקה משה ואלי חולי – כמו פעם</v>
+        <v>שלומית אהרון – פיסות אהבה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>תמר גלעדי קרני פוסטל שאול בסר – רוצי מריה</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://yosmusic.com/%d7%aa%d7%9e%d7%a8-%d7%92%d7%9c%d7%a2%d7%93%d7%99-%d7%a7%d7%a8%d7%a0%d7%99-%d7%a4%d7%95%d7%a1%d7%98%d7%9c-%d7%a9%d7%90%d7%95%d7%9c-%d7%91%d7%a1%d7%a8-%d7%a8%d7%95%d7%a6%d7%99-%d7%9e%d7%a8%d7%99%d7%94/</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>השיר “רוצי מריה” כשמבוצע על ידי תמר גלעדי בליווי קרני פוסטל ושאול בסר הוא יצירה שממוקמת על התפר שבין שיר אמנותי (art song) לבין בלדה פופולרית מינורית-קלאסית. זהו ביצוע שמבוסס על לחן של קרלוס אנטוניו ז’ובים (Tom Jobim), כאשר הטקסט</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>תמר גלעדי קרני פוסטל שאול בסר – רוצי מריה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומית אהרון – פיסות אהבה</v>
+        <v>יובל גולד ושירה זלוף – מחר יבוא מחר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%9e%d7%99%d7%aa-%d7%90%d7%94%d7%a8%d7%95%d7%9f-%d7%a4%d7%99%d7%a1%d7%95%d7%aa-%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%92%d7%95%d7%9c%d7%93-%d7%95%d7%a9%d7%99%d7%a8%d7%94-%d7%96%d7%9c%d7%95%d7%a3-%d7%9e%d7%97%d7%a8-%d7%99%d7%91%d7%95%d7%90-%d7%9e%d7%97%d7%a8/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>שלומית אהרון מגישה ב־"פיסות אהבה" שיר שנשען על מסורת הפופ המלודי הקלאסי של שנות ה־70 וה־80. . זהו שיר שמחבר בין אסתטיקה “אולד סקול” לבין חרדה קיומית,  והחיבור הזה הוא מקור הכוח שלו. צליל האקורדיון בפתיחה מייצר אווירת שנסון אירופי</v>
+        <v>השיר "מחר יבוא מחר" של יובל גולד ושירה זלוף מצליח משלב בין פופ עכשווי, רגש חשוף ואווירה ישראלית של חוסר יציבות – גם בזוגיות וגם בחיים עצמם. החיבור בין שני בוגרי הכוכב הבא יוצר דואט שמרגיש טבעי ולא מתאמץ, כמעט</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומית אהרון – פיסות אהבה</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>תמר גלעדי קרני פוסטל שאול בסר – רוצי מריה</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-19</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%aa%d7%9e%d7%a8-%d7%92%d7%9c%d7%a2%d7%93%d7%99-%d7%a7%d7%a8%d7%a0%d7%99-%d7%a4%d7%95%d7%a1%d7%98%d7%9c-%d7%a9%d7%90%d7%95%d7%9c-%d7%91%d7%a1%d7%a8-%d7%a8%d7%95%d7%a6%d7%99-%d7%9e%d7%a8%d7%99%d7%94/</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-19</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>השיר “רוצי מריה” כשמבוצע על ידי תמר גלעדי בליווי קרני פוסטל ושאול בסר הוא יצירה שממוקמת על התפר שבין שיר אמנותי (art song) לבין בלדה פופולרית מינורית-קלאסית. זהו ביצוע שמבוסס על לחן של קרלוס אנטוניו ז’ובים (Tom Jobim), כאשר הטקסט</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>תמר גלעדי קרני פוסטל שאול בסר – רוצי מריה</v>
+        <v>יובל גולד ושירה זלוף – מחר יבוא מחר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל גולד ושירה זלוף – מחר יבוא מחר</v>
+        <v>יוני רכטר ואלי דג׳יברי – זו אותה האהבה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-20</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%92%d7%95%d7%9c%d7%93-%d7%95%d7%a9%d7%99%d7%a8%d7%94-%d7%96%d7%9c%d7%95%d7%a3-%d7%9e%d7%97%d7%a8-%d7%99%d7%91%d7%95%d7%90-%d7%9e%d7%97%d7%a8/</v>
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%a0%d7%99-%d7%a8%d7%9b%d7%98%d7%a8-%d7%95%d7%90%d7%9c%d7%99-%d7%93%d7%92%d7%b3%d7%99%d7%91%d7%a8%d7%99-%d7%96%d7%95-%d7%90%d7%95%d7%aa%d7%94-%d7%94%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-20</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "מחר יבוא מחר" של יובל גולד ושירה זלוף מצליח משלב בין פופ עכשווי, רגש חשוף ואווירה ישראלית של חוסר יציבות – גם בזוגיות וגם בחיים עצמם. החיבור בין שני בוגרי הכוכב הבא יוצר דואט שמרגיש טבעי ולא מתאמץ, כמעט</v>
+        <v>הקאבר החדש של יוני רכטר ואלי דג'יברי ל־"זו אותה האהבה" אינו רק ביצוע מחודש לשירו הקלאסי של אריק איינשטיין  אלא גרסה בוגרת ואינטימית לטקסט שנשמע היום כמעט עמוק יותר משהיה בזמן שנכתב.זהו ביצוע שמוותר על נוסטלגיה "גדולה מהחיים", ובוחר במקום</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל גולד ושירה זלוף – מחר יבוא מחר</v>
+        <v>יוני רכטר ואלי דג׳יברי – זו אותה האהבה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יוני רכטר ואלי דג׳יברי – זו אותה האהבה</v>
+        <v>עדן בן זקן &amp; נועה קירל – אני משקרת?</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%a0%d7%99-%d7%a8%d7%9b%d7%98%d7%a8-%d7%95%d7%90%d7%9c%d7%99-%d7%93%d7%92%d7%b3%d7%99%d7%91%d7%a8%d7%99-%d7%96%d7%95-%d7%90%d7%95%d7%aa%d7%94-%d7%94%d7%90%d7%94%d7%91%d7%94/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%91%d7%9f-%d7%96%d7%a7%d7%9f-%d7%a0%d7%95%d7%a2%d7%94-%d7%a7%d7%99%d7%a8%d7%9c-%d7%90%d7%a0%d7%99-%d7%9e%d7%a9%d7%a7%d7%a8%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הקאבר החדש של יוני רכטר ואלי דג'יברי ל־"זו אותה האהבה" אינו רק ביצוע מחודש לשירו הקלאסי של אריק איינשטיין  אלא גרסה בוגרת ואינטימית לטקסט שנשמע היום כמעט עמוק יותר משהיה בזמן שנכתב.זהו ביצוע שמוותר על נוסטלגיה "גדולה מהחיים", ובוחר במקום</v>
+        <v>השיר “אני משקרת?” של נועה קירל ועדן בן זקן מרגיש כמעט כמו ניסוי מעבדה בפופ ישראלי של 2026.  לוקחים שתי מכונות־להיטים עם פרסונות שונות, מערבבים הומור אינטרנטי, אסתטיקת AI, מזרחית־פופ־דאנס, ומוציאים מוצר שנשמע בו־זמנית מודע לעצמו וציני כלפי עצם הרעיון</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יוני רכטר ואלי דג׳יברי – זו אותה האהבה</v>
+        <v>עדן בן זקן &amp; נועה קירל – אני משקרת?</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עדן בן זקן &amp; נועה קירל – אני משקרת?</v>
+        <v>עדן חסון &amp; אופק אדנק מארחים את אגם בוחבוט – איך שהיא רוקדת</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-21</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%91%d7%9f-%d7%96%d7%a7%d7%9f-%d7%a0%d7%95%d7%a2%d7%94-%d7%a7%d7%99%d7%a8%d7%9c-%d7%90%d7%a0%d7%99-%d7%9e%d7%a9%d7%a7%d7%a8%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%97%d7%a1%d7%95%d7%9f-%d7%90%d7%95%d7%a4%d7%a7-%d7%90%d7%93%d7%a0%d7%a7-%d7%9e%d7%90%d7%a8%d7%97%d7%99%d7%9d-%d7%90%d7%aa-%d7%90%d7%92%d7%9d-%d7%91%d7%95%d7%97%d7%91%d7%95/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-21</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר “אני משקרת?” של נועה קירל ועדן בן זקן מרגיש כמעט כמו ניסוי מעבדה בפופ ישראלי של 2026.  לוקחים שתי מכונות־להיטים עם פרסונות שונות, מערבבים הומור אינטרנטי, אסתטיקת AI, מזרחית־פופ־דאנס, ומוציאים מוצר שנשמע בו־זמנית מודע לעצמו וציני כלפי עצם הרעיון</v>
+        <v>השיר "איך שהיא רוקדת" של עדן חסון ואופק אדנק יחד עם אגם בוחבוט בנוי כמעט באופן מובהק כ"להיט קיץ" ישראלי עכשווי, כזה שמכוון לפלייליסטים, נסיעות, מסיבות ובריכות. אבל מתחת לקלילות שלו יש כמה שכבות מעניינות מבחינה מוזיקלית והפקתית. כבר מהשורות:</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עדן בן זקן &amp; נועה קירל – אני משקרת?</v>
+        <v>עדן חסון &amp; אופק אדנק מארחים את אגם בוחבוט – איך שהיא רוקדת</v>
       </c>
     </row>
   </sheetData>
